--- a/tools/sheets/npc.xlsx
+++ b/tools/sheets/npc.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -452,60 +452,65 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>name_color</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>traits</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>flee_chance</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>walk_speed</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>run_speed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>strength</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>endurance</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>intelligence</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>health</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>mental</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>divinity</t>
         </is>
@@ -524,12 +529,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>#F2C200</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
@@ -543,6 +550,9 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -559,12 +569,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>#4FC3F7</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
@@ -578,6 +590,9 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -594,12 +609,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>#E8B04A</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
@@ -613,6 +630,9 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -627,18 +647,20 @@
           <t>적 A (테스트)</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>monster</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>50</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>3.2</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
@@ -652,6 +674,9 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1076,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1152,6 +1177,14 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Npcs.kind: monster(몬스터 — 맵에 '적'으로 놓으면 마주치자마자 전투) / npc(사람·동물 등, 비우면 npc). 둘 다 전투 중 '대화' 가능 (그 NPC 대화의 ▶ 대화 시작 카드에서 '전투 중이다' 길로)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/sheets/npc.xlsx
+++ b/tools/sheets/npc.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,6 +437,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,6 +514,11 @@
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>divinity</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>battle_bt</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1183,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
